--- a/public/downloads/BalzarettiDensity2024.xlsx
+++ b/public/downloads/BalzarettiDensity2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>N</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>69</v>
       </c>
       <c r="N3" s="5">
-        <v>517.489226102829</v>
+        <v>517489.226102829</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03271728052745963</v>
+        <v>32.71728052745964</v>
       </c>
       <c r="P3" s="5">
         <v>15817</v>
@@ -709,10 +732,10 @@
         <v>69</v>
       </c>
       <c r="N4" s="5">
-        <v>271.9837234020233</v>
+        <v>271983.7234020233</v>
       </c>
       <c r="O4" s="4">
-        <v>0.0345947244215242</v>
+        <v>34.59472442152421</v>
       </c>
       <c r="P4" s="5">
         <v>7862</v>
@@ -759,10 +782,10 @@
         <v>69</v>
       </c>
       <c r="N5" s="5">
-        <v>659.600813627243</v>
+        <v>659600.813627243</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1284019493142385</v>
+        <v>128.4019493142385</v>
       </c>
       <c r="P5" s="5">
         <v>5137</v>
@@ -809,10 +832,10 @@
         <v>69</v>
       </c>
       <c r="N6" s="5">
-        <v>673.6615800857544</v>
+        <v>673661.5800857544</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1026766621072633</v>
+        <v>102.6766621072633</v>
       </c>
       <c r="P6" s="5">
         <v>6561</v>
@@ -859,10 +882,10 @@
         <v>69</v>
       </c>
       <c r="N7" s="5">
-        <v>1480.386652231216</v>
+        <v>1480386.652231216</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1485288102971021</v>
+        <v>148.5288102971021</v>
       </c>
       <c r="P7" s="5">
         <v>9967</v>
@@ -909,10 +932,10 @@
         <v>69</v>
       </c>
       <c r="N8" s="5">
-        <v>80.40255975723267</v>
+        <v>80402.55975723267</v>
       </c>
       <c r="O8" s="4">
-        <v>0.009875038044366577</v>
+        <v>9.875038044366578</v>
       </c>
       <c r="P8" s="5">
         <v>8142</v>
@@ -959,10 +982,10 @@
         <v>69</v>
       </c>
       <c r="N9" s="5">
-        <v>149.0111477375031</v>
+        <v>149011.1477375031</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02760488101843332</v>
+        <v>27.60488101843332</v>
       </c>
       <c r="P9" s="5">
         <v>5398</v>
@@ -1009,10 +1032,10 @@
         <v>69</v>
       </c>
       <c r="N10" s="5">
-        <v>276.8720438480377</v>
+        <v>276872.0438480377</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08189057789057608</v>
+        <v>81.89057789057608</v>
       </c>
       <c r="P10" s="5">
         <v>3381</v>
@@ -1059,10 +1082,10 @@
         <v>69</v>
       </c>
       <c r="N11" s="5">
-        <v>906.802549123764</v>
+        <v>906802.549123764</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04272533684148907</v>
+        <v>42.72533684148907</v>
       </c>
       <c r="P11" s="5">
         <v>21224</v>
@@ -1109,10 +1132,10 @@
         <v>69</v>
       </c>
       <c r="N12" s="5">
-        <v>153.1037390232086</v>
+        <v>153103.7390232086</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01618432759230535</v>
+        <v>16.18432759230535</v>
       </c>
       <c r="P12" s="5">
         <v>9460</v>
@@ -1159,10 +1182,10 @@
         <v>69</v>
       </c>
       <c r="N13" s="5">
-        <v>1239.405383825302</v>
+        <v>1239405.383825302</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08032439298932613</v>
+        <v>80.32439298932613</v>
       </c>
       <c r="P13" s="5">
         <v>15430</v>
@@ -1209,10 +1232,10 @@
         <v>69</v>
       </c>
       <c r="N14" s="5">
-        <v>368.7506034374237</v>
+        <v>368750.6034374237</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2084514434355137</v>
+        <v>208.4514434355137</v>
       </c>
       <c r="P14" s="5">
         <v>1769</v>
@@ -1259,10 +1282,10 @@
         <v>69</v>
       </c>
       <c r="N15" s="5">
-        <v>707.0555818080902</v>
+        <v>707055.5818080902</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2083865552042706</v>
+        <v>208.3865552042706</v>
       </c>
       <c r="P15" s="5">
         <v>3393</v>
@@ -1309,10 +1332,10 @@
         <v>69</v>
       </c>
       <c r="N16" s="5">
-        <v>260.0325660705566</v>
+        <v>260032.5660705566</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1187905738102132</v>
+        <v>118.7905738102132</v>
       </c>
       <c r="P16" s="5">
         <v>2189</v>
@@ -1359,10 +1382,10 @@
         <v>69</v>
       </c>
       <c r="N17" s="5">
-        <v>617.8228294849396</v>
+        <v>617822.8294849396</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1052688412821502</v>
+        <v>105.2688412821502</v>
       </c>
       <c r="P17" s="5">
         <v>5869</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2785335674082489</v>
+        <v>0.1851081082371001</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2741661518671482</v>
+        <v>0.1851081082371001</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2889698414113523</v>
+        <v>0.1745217180786468</v>
       </c>
       <c r="E3" s="4">
-        <v>80.42147293700059</v>
+        <v>93.09671694764862</v>
       </c>
       <c r="F3" s="4">
-        <v>89.25347728820252</v>
+        <v>95.93230230522323</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.182212868598397</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08823448263430791</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08823448263430791</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.133831791332697</v>
+        <v>0.232226528717748</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1378170668167421</v>
+        <v>0.2185640706194011</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1307952603573646</v>
+        <v>0.201713706125483</v>
       </c>
       <c r="E4" s="4">
-        <v>80.8873114463178</v>
+        <v>91.29991126885541</v>
       </c>
       <c r="F4" s="4">
-        <v>90.24997568329921</v>
+        <v>92.25707615990707</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1872295854344532</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.176347151067806</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1509662314510059</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1534668707450171</v>
+        <v>2.752262695312993</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1490840986748287</v>
+        <v>0.1865375278308645</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1405895021735825</v>
+        <v>4.870280901939317</v>
       </c>
       <c r="E5" s="4">
-        <v>79.83141082519958</v>
+        <v>83.32298136645983</v>
       </c>
       <c r="F5" s="4">
-        <v>89.01955062737089</v>
+        <v>85.53545374963238</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.5431466319978376</v>
+      </c>
+      <c r="O5" s="5">
+        <v>18</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.827233568209384</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4796675201016884</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,75 +1797,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3768869856822152</v>
+        <v>0.4027693509270174</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4070937827106942</v>
+        <v>0.4027693509270174</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3748681485407815</v>
+        <v>0.3351364881088384</v>
       </c>
       <c r="E3" s="4">
-        <v>90.40816326530602</v>
+        <v>88.1366459627329</v>
       </c>
       <c r="F3" s="4">
-        <v>92.14327400058313</v>
+        <v>91.11321855850579</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4027693509270174</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1976753281909036</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1976753281909036</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4144274747709302</v>
+        <v>0.5137508471422834</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4144274747709302</v>
+        <v>0.4771818723733058</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3852802326551863</v>
+        <v>0.5066022427958368</v>
       </c>
       <c r="E4" s="4">
-        <v>90.05175983436855</v>
+        <v>85.36527654540072</v>
       </c>
       <c r="F4" s="4">
-        <v>92.41708005057822</v>
+        <v>89.62357747300908</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1755,50 +1915,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.374320673746147</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4464686863409985</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3957350461401714</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>9.194777748040934</v>
+        <v>2.124213279057243</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3180048539022347</v>
+        <v>0.6176548895079019</v>
       </c>
       <c r="D5" s="4">
-        <v>10.65599395180442</v>
+        <v>2.886842912421713</v>
       </c>
       <c r="E5" s="4">
-        <v>83.71783496007124</v>
+        <v>84.92014196983054</v>
       </c>
       <c r="F5" s="4">
-        <v>88.14560840385099</v>
+        <v>88.65334111467934</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.048868717983847</v>
+      </c>
+      <c r="O5" s="5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.785345450467943</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.624871002076417</v>
+      </c>
+      <c r="R5" s="5">
         <v>17</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>4</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="S5" s="5">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4989567118312689</v>
+        <v>0.133831791332697</v>
       </c>
       <c r="C3" s="4">
-        <v>0.486194664158147</v>
+        <v>0.1378170668167421</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4188586840629265</v>
+        <v>0.1307952603573646</v>
       </c>
       <c r="E3" s="4">
-        <v>86.94912747707778</v>
+        <v>80.8873114463178</v>
       </c>
       <c r="F3" s="4">
-        <v>88.80118665499542</v>
+        <v>90.24997568329921</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07626561580252558</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1303484382656246</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1267385738573271</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3403551919815191</v>
+        <v>0.2785335674082489</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3403551919815191</v>
+        <v>0.2741661518671482</v>
       </c>
       <c r="D4" s="4">
-        <v>0.322298073690079</v>
+        <v>0.2889698414113523</v>
       </c>
       <c r="E4" s="4">
-        <v>90.03549245785268</v>
+        <v>80.42147293700059</v>
       </c>
       <c r="F4" s="4">
-        <v>94.15231981324774</v>
+        <v>89.25347728820252</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1226424180680183</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2289657270981218</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2081973345686264</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>4.596190463816077</v>
+        <v>0.1534668707450171</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2776791728976447</v>
+        <v>0.1490840986748287</v>
       </c>
       <c r="D5" s="4">
-        <v>5.028269586362621</v>
+        <v>0.1405895021735825</v>
       </c>
       <c r="E5" s="4">
-        <v>87.20644779650951</v>
+        <v>79.83141082519958</v>
       </c>
       <c r="F5" s="4">
-        <v>89.98200564147598</v>
+        <v>89.01955062737089</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.0419243259153981</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1408247833470345</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1352380029532288</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2397,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3444558626010559</v>
+        <v>0.4144274747709302</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3188469007728184</v>
+        <v>0.4144274747709302</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3124508714109228</v>
+        <v>0.3852802326551863</v>
       </c>
       <c r="E3" s="4">
-        <v>89.9511978704525</v>
+        <v>90.05175983436855</v>
       </c>
       <c r="F3" s="4">
-        <v>93.77054761210007</v>
+        <v>92.41708005057822</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2140,66 +2456,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3316743715164313</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3095483827496257</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3095483827496257</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3581623128437336</v>
+        <v>0.3768869856822152</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3581623128437336</v>
+        <v>0.4070937827106942</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3498867417669673</v>
+        <v>0.3748681485407815</v>
       </c>
       <c r="E4" s="4">
-        <v>90.63886424134873</v>
+        <v>90.40816326530602</v>
       </c>
       <c r="F4" s="4">
-        <v>95.38955354537497</v>
+        <v>92.14327400058313</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2269727443281266</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3125807646751658</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3286708917709955</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.552354220825677</v>
+        <v>9.194777748040934</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1676793857892261</v>
+        <v>0.3180048539022347</v>
       </c>
       <c r="D5" s="4">
-        <v>6.410681215680148</v>
+        <v>10.65599395180442</v>
       </c>
       <c r="E5" s="4">
-        <v>79.66873706004144</v>
+        <v>83.71783496007124</v>
       </c>
       <c r="F5" s="4">
-        <v>83.7389359011779</v>
+        <v>88.14560840385099</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
@@ -2208,23 +2560,41 @@
         <v>17</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.03337470438476357</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>9.186830853523697</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3190324805147118</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,81 +2697,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2763322336452273</v>
+        <v>0.3403551919815191</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1483816024130154</v>
+        <v>0.3403551919815191</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1815354871619117</v>
+        <v>0.322298073690079</v>
       </c>
       <c r="E3" s="4">
-        <v>93.4501626737644</v>
+        <v>90.03549245785268</v>
       </c>
       <c r="F3" s="4">
-        <v>96.05096780468779</v>
+        <v>94.15231981324774</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3403551919815191</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1448267282279797</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1448267282279797</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1544919059904203</v>
+        <v>0.4989567118312689</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06449011931080913</v>
+        <v>0.486194664158147</v>
       </c>
       <c r="D4" s="4">
-        <v>0.06467553801039787</v>
+        <v>0.4188586840629265</v>
       </c>
       <c r="E4" s="4">
-        <v>94.33007985802945</v>
+        <v>86.94912747707778</v>
       </c>
       <c r="F4" s="4">
-        <v>97.39616768796782</v>
+        <v>88.80118665499542</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>1</v>
@@ -2394,50 +2815,84 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.486194664158147</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1769514075920509</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1795171923741293</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2263823108174519</v>
+        <v>4.596190463816077</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1280191588411941</v>
+        <v>0.2776791728976447</v>
       </c>
       <c r="D5" s="4">
-        <v>0.12896213537911</v>
+        <v>5.028269586362621</v>
       </c>
       <c r="E5" s="4">
-        <v>94.50754214729301</v>
+        <v>87.20644779650951</v>
       </c>
       <c r="F5" s="4">
-        <v>97.28479719871578</v>
+        <v>89.98200564147598</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="N5" s="4">
+        <v>3.481150424272764</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>6.259767387034104</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2903,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2922,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2964,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,37 +2995,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7196638225679478</v>
+        <v>0.3581623128437336</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6099761514346599</v>
+        <v>0.3581623128437336</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7758166152964133</v>
+        <v>0.3498867417669673</v>
       </c>
       <c r="E3" s="4">
-        <v>88.24460218870161</v>
+        <v>90.63886424134873</v>
       </c>
       <c r="F3" s="4">
-        <v>92.90925007294989</v>
+        <v>95.38955354537497</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -2564,27 +3052,45 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3581623128437336</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07488897875347074</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07488897875347074</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4399092111113138</v>
+        <v>0.3444558626010559</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3597307644145777</v>
+        <v>0.3188469007728184</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5145285043242044</v>
+        <v>0.3124508714109228</v>
       </c>
       <c r="E4" s="4">
-        <v>89.63176574977818</v>
+        <v>89.9511978704525</v>
       </c>
       <c r="F4" s="4">
-        <v>94.83367376714327</v>
+        <v>93.77054761210007</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
@@ -2593,10 +3099,10 @@
         <v>22</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2605,42 +3111,60 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3181818992112052</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1860634607847836</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.167717657929043</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5073339764882946</v>
+        <v>2.552354220825677</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4750851618731469</v>
+        <v>0.1676793857892261</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7701033111558252</v>
+        <v>6.410681215680148</v>
       </c>
       <c r="E5" s="4">
-        <v>87.55989352262587</v>
+        <v>79.66873706004144</v>
       </c>
       <c r="F5" s="4">
-        <v>92.20601108841745</v>
+        <v>83.7389359011779</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2648,9 +3172,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.139719624327251</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.563642963020406</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1336395813489485</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3203,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3222,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3264,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,34 +3295,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2685969162587434</v>
+        <v>0.1544919059904203</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1449394112314445</v>
+        <v>0.06449011931080913</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1726863010115146</v>
+        <v>0.06467553801039787</v>
       </c>
       <c r="E3" s="4">
-        <v>89.51049985211398</v>
+        <v>94.33007985802945</v>
       </c>
       <c r="F3" s="4">
-        <v>94.48983561910252</v>
+        <v>97.39616768796782</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2779,34 +3354,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05520139841579592</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1340293774571558</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04560663031765973</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1464958961513124</v>
+        <v>0.2763322336452273</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06154054137020619</v>
+        <v>0.1483816024130154</v>
       </c>
       <c r="D4" s="4">
-        <v>0.06241888265928443</v>
+        <v>0.1815354871619117</v>
       </c>
       <c r="E4" s="4">
-        <v>90.21295474711548</v>
+        <v>93.4501626737644</v>
       </c>
       <c r="F4" s="4">
-        <v>95.76159906623833</v>
+        <v>96.05096780468779</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -2820,25 +3413,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1476921415309912</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2240592256819597</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1051961309800072</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1904539858201409</v>
+        <v>0.2263823108174519</v>
       </c>
       <c r="C5" s="4">
-        <v>0.09963027610946386</v>
+        <v>0.1280191588411941</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09493153545598655</v>
+        <v>0.12896213537911</v>
       </c>
       <c r="E5" s="4">
-        <v>90.50133096716878</v>
+        <v>94.50754214729301</v>
       </c>
       <c r="F5" s="4">
-        <v>95.5641474564727</v>
+        <v>97.28479719871578</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
@@ -2861,9 +3472,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1172092755845865</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1612668615911582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06527161081300464</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3503,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3522,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3564,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,37 +3595,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5493605858072492</v>
+        <v>0.4399092111113138</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5375750387178257</v>
+        <v>0.3597307644145777</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5293090332484475</v>
+        <v>0.5145285043242044</v>
       </c>
       <c r="E3" s="4">
-        <v>85.1626737651582</v>
+        <v>89.63176574977818</v>
       </c>
       <c r="F3" s="4">
-        <v>90.74263203968474</v>
+        <v>94.83367376714327</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -2990,39 +3652,57 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4399092111113138</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1591186579052093</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1591186579052093</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.255371924686611</v>
+        <v>0.7196638225679478</v>
       </c>
       <c r="C4" s="4">
-        <v>0.255371924686611</v>
+        <v>0.6099761514346599</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2603292289762208</v>
+        <v>0.7758166152964133</v>
       </c>
       <c r="E4" s="4">
-        <v>86.43744454303456</v>
+        <v>88.24460218870161</v>
       </c>
       <c r="F4" s="4">
-        <v>93.23168952436524</v>
+        <v>92.90925007294989</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -3031,52 +3711,88 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.7041955100076979</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1918162534185378</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1843637563518463</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.419391797457728</v>
+        <v>0.5073339764882946</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2951532783968207</v>
+        <v>0.4750851618731469</v>
       </c>
       <c r="D5" s="4">
-        <v>4.183818378695355</v>
+        <v>0.7701033111558252</v>
       </c>
       <c r="E5" s="4">
-        <v>79.31972789115621</v>
+        <v>87.55989352262587</v>
       </c>
       <c r="F5" s="4">
-        <v>84.57348506954489</v>
+        <v>92.20601108841745</v>
       </c>
       <c r="G5" s="5">
         <v>23</v>
       </c>
       <c r="H5" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4750851618731469</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1526657153039152</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08270083600433459</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3803,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1464958961513124</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.06154054137020619</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.06241888265928443</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.21295474711548</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.76159906623833</v>
+      </c>
+      <c r="G3" s="5">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04767936505763382</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1335299633638813</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05015249186778432</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2685969162587434</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1449394112314445</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1726863010115146</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.51049985211398</v>
+      </c>
+      <c r="F4" s="4">
+        <v>94.48983561910252</v>
+      </c>
+      <c r="G4" s="5">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1173206753229193</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2316573085906362</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1156551433399861</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1904539858201409</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.09963027610946386</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.09493153545598655</v>
+      </c>
+      <c r="E5" s="4">
+        <v>90.50133096716878</v>
+      </c>
+      <c r="F5" s="4">
+        <v>95.5641474564727</v>
+      </c>
+      <c r="G5" s="5">
+        <v>23</v>
+      </c>
+      <c r="H5" s="5">
+        <v>22</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.06491039108442974</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1645768239541577</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07552735193522823</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.255371924686611</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.255371924686611</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2603292289762208</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.43744454303456</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.23168952436524</v>
+      </c>
+      <c r="G3" s="5">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2442022670084874</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1083722513008634</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1083722513008634</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5493605858072492</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5375750387178257</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5293090332484475</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.1626737651582</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.74263203968474</v>
+      </c>
+      <c r="G4" s="5">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5297754165652819</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1924058644224035</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1856893929280466</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2.419391797457728</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2951532783968207</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4.183818378695355</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.31972789115621</v>
+      </c>
+      <c r="F5" s="4">
+        <v>84.57348506954489</v>
+      </c>
+      <c r="G5" s="5">
+        <v>23</v>
+      </c>
+      <c r="H5" s="5">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.8531979573462709</v>
+      </c>
+      <c r="O5" s="5">
+        <v>18</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.887234934402152</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.131839667128553</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="D3" s="3">
+        <v>7.246376811594203</v>
+      </c>
+      <c r="E3" s="3">
+        <v>7.246376811594203</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.776647101952246</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1498864687372405</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.632486651926779</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.45144434585463</v>
+      </c>
+      <c r="L3" s="4">
+        <v>90.77391952793167</v>
+      </c>
+      <c r="M3" s="5">
+        <v>69</v>
+      </c>
+      <c r="N3" s="5">
+        <v>517489.226102829</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.71728052745964</v>
+      </c>
+      <c r="P3" s="5">
+        <v>15817</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3843793991145523</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3613204540438006</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3731930175369899</v>
+      </c>
+      <c r="K4" s="4">
+        <v>89.1195898649316</v>
+      </c>
+      <c r="L4" s="4">
+        <v>90.41289757805735</v>
+      </c>
+      <c r="M4" s="5">
+        <v>69</v>
+      </c>
+      <c r="N4" s="5">
+        <v>271983.7234020233</v>
+      </c>
+      <c r="O4" s="4">
+        <v>34.59472442152421</v>
+      </c>
+      <c r="P4" s="5">
+        <v>7862</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>84.05797101449275</v>
+      </c>
+      <c r="C5" s="3">
+        <v>10.14492753623188</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.223464773038928</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.5263883303407146</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.803729911823445</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.8135660061122</v>
+      </c>
+      <c r="L5" s="4">
+        <v>91.09635897934758</v>
+      </c>
+      <c r="M5" s="5">
+        <v>69</v>
+      </c>
+      <c r="N5" s="5">
+        <v>659600.813627243</v>
+      </c>
+      <c r="O5" s="4">
+        <v>128.4019493142385</v>
+      </c>
+      <c r="P5" s="5">
+        <v>5137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15.94202898550724</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1.000383148258783</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3625940862643418</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1.279385280349065</v>
+      </c>
+      <c r="K6" s="4">
+        <v>85.21887015675816</v>
+      </c>
+      <c r="L6" s="4">
+        <v>87.73173815776715</v>
+      </c>
+      <c r="M6" s="5">
+        <v>69</v>
+      </c>
+      <c r="N6" s="5">
+        <v>673661.5800857544</v>
+      </c>
+      <c r="O6" s="4">
+        <v>102.6766621072633</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="D7" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="G7" s="3">
+        <v>28.98550724637681</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2.231182526509278</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.08104798241745767</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.473244452480268</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.33629103815387</v>
+      </c>
+      <c r="L7" s="4">
+        <v>95.08040722368314</v>
+      </c>
+      <c r="M7" s="5">
+        <v>69</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1480386.652231216</v>
+      </c>
+      <c r="O7" s="4">
+        <v>148.5288102971021</v>
+      </c>
+      <c r="P7" s="5">
+        <v>9967</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7.246376811594203</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.030605067303833</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2200510928556317</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.721233833278414</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.2398698609876</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91.24161073825476</v>
+      </c>
+      <c r="M8" s="5">
+        <v>69</v>
+      </c>
+      <c r="N8" s="5">
+        <v>80402.55975723267</v>
+      </c>
+      <c r="O8" s="4">
+        <v>9.875038044366578</v>
+      </c>
+      <c r="P8" s="5">
+        <v>8142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>85.50724637681159</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.59420289855072</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.8098298216666148</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3845475501754768</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1.048212772214983</v>
+      </c>
+      <c r="K9" s="4">
+        <v>86.14068815932139</v>
+      </c>
+      <c r="L9" s="4">
+        <v>89.79671238206683</v>
+      </c>
+      <c r="M9" s="5">
+        <v>69</v>
+      </c>
+      <c r="N9" s="5">
+        <v>149011.1477375031</v>
+      </c>
+      <c r="O9" s="4">
+        <v>27.60488101843332</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1667129829035937</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1567246371263941</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1658106429217215</v>
+      </c>
+      <c r="K10" s="4">
+        <v>80.38006506950582</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.50766786629111</v>
+      </c>
+      <c r="M10" s="5">
+        <v>69</v>
+      </c>
+      <c r="N10" s="5">
+        <v>276872.0438480377</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.89057789057608</v>
+      </c>
+      <c r="P10" s="5">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10.14492753623188</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3.269653333649496</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3186097134568567</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3.77266916027253</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.05925268658189</v>
+      </c>
+      <c r="L11" s="4">
+        <v>90.90198748500588</v>
+      </c>
+      <c r="M11" s="5">
+        <v>69</v>
+      </c>
+      <c r="N11" s="5">
+        <v>906802.549123764</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.72533684148907</v>
+      </c>
+      <c r="P11" s="5">
+        <v>21224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>57.97101449275362</v>
+      </c>
+      <c r="C12" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D12" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="G12" s="3">
+        <v>28.98550724637681</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2.193848507618045</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1595701754900933</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2.335534379116866</v>
+      </c>
+      <c r="K12" s="4">
+        <v>88.0636892438132</v>
+      </c>
+      <c r="L12" s="4">
+        <v>90.9785040365752</v>
+      </c>
+      <c r="M12" s="5">
+        <v>69</v>
+      </c>
+      <c r="N12" s="5">
+        <v>153103.7390232086</v>
+      </c>
+      <c r="O12" s="4">
+        <v>16.18432759230535</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>89.85507246376811</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.246376811594203</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7.246376811594203</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.9415318008528869</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1239372236887241</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.220441904580213</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.75293305728061</v>
+      </c>
+      <c r="L13" s="4">
+        <v>90.96634568621863</v>
+      </c>
+      <c r="M13" s="5">
+        <v>69</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1239405.383825302</v>
+      </c>
+      <c r="O13" s="4">
+        <v>80.32439298932613</v>
+      </c>
+      <c r="P13" s="5">
+        <v>15430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>94.20289855072464</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1731184882434246</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.07151446239161181</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.08056084749832358</v>
+      </c>
+      <c r="K14" s="4">
+        <v>94.09592822636226</v>
+      </c>
+      <c r="L14" s="4">
+        <v>96.91064423045749</v>
+      </c>
+      <c r="M14" s="5">
+        <v>69</v>
+      </c>
+      <c r="N14" s="5">
+        <v>368750.6034374237</v>
+      </c>
+      <c r="O14" s="4">
+        <v>208.4514434355137</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>97.10144927536231</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1678668755425541</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1423156740844149</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.312975710477976</v>
+      </c>
+      <c r="K15" s="4">
+        <v>88.47875382036879</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.31631164283876</v>
+      </c>
+      <c r="M15" s="5">
+        <v>69</v>
+      </c>
+      <c r="N15" s="5">
+        <v>707055.5818080902</v>
+      </c>
+      <c r="O15" s="4">
+        <v>208.3865552042706</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>94.20289855072464</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1765880319695585</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.0799033011354767</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.0865688775513561</v>
+      </c>
+      <c r="K16" s="4">
+        <v>90.07492852213281</v>
+      </c>
+      <c r="L16" s="4">
+        <v>95.27186071393811</v>
+      </c>
+      <c r="M16" s="5">
+        <v>69</v>
+      </c>
+      <c r="N16" s="5">
+        <v>260032.5660705566</v>
+      </c>
+      <c r="O16" s="4">
+        <v>118.7905738102132</v>
+      </c>
+      <c r="P16" s="5">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.50724637681159</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5.797101449275362</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.449275362318841</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2.898550724637681</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.062671016708473</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.412131937500638</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.625687578605793</v>
+      </c>
+      <c r="K17" s="4">
+        <v>83.63994873311621</v>
+      </c>
+      <c r="L17" s="4">
+        <v>89.51593554453008</v>
+      </c>
+      <c r="M17" s="5">
+        <v>69</v>
+      </c>
+      <c r="N17" s="5">
+        <v>617822.8294849396</v>
+      </c>
+      <c r="O17" s="4">
+        <v>105.2688412821502</v>
+      </c>
+      <c r="P17" s="5">
+        <v>5869</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3385,7 +5559,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3558,10 +5732,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L11" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3602,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" s="5">
         <v>0</v>
@@ -3646,10 +5820,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3737,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -3825,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>60</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>58</v>
+      </c>
+      <c r="C5" s="5">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>54</v>
+      </c>
+      <c r="C6" s="5">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>60</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>59</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>63</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>6</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>60</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5">
+        <v>4</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>3</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>40</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5">
+        <v>23</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>20</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>62</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>65</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>3</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>65</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>59</v>
+      </c>
+      <c r="C17" s="5">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,34 +6862,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2580115563234568</v>
+        <v>0.2576568053330923</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2233090103793966</v>
+        <v>0.2576568053330923</v>
       </c>
       <c r="D3" s="4">
-        <v>0.200208700914998</v>
+        <v>0.2280178237472404</v>
       </c>
       <c r="E3" s="4">
-        <v>89.393670511683</v>
+        <v>91.97870452528836</v>
       </c>
       <c r="F3" s="4">
-        <v>91.9244236941928</v>
+        <v>94.52290633206866</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -3960,34 +6921,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2576568053330923</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08962835366822133</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08962835366822133</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2576568053330923</v>
+        <v>0.2580115563234568</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2576568053330923</v>
+        <v>0.2233090103793966</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2280178237472404</v>
+        <v>0.200208700914998</v>
       </c>
       <c r="E4" s="4">
-        <v>91.97870452528836</v>
+        <v>89.393670511683</v>
       </c>
       <c r="F4" s="4">
-        <v>94.52290633206866</v>
+        <v>91.9244236941928</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2101089213911148</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1813410370505492</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.16665425142422</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>5.181442295061567</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2678435010587066</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>5.058971915137966</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2116853506694671</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,92 +7162,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.486913551463572</v>
+        <v>0.2541875520213244</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4445784556657875</v>
+        <v>0.255205264211658</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3903564318452806</v>
+        <v>0.2105341334847612</v>
       </c>
       <c r="E3" s="4">
-        <v>88.66015971606035</v>
+        <v>89.30641821946168</v>
       </c>
       <c r="F3" s="4">
-        <v>89.12994844859698</v>
+        <v>90.04036572317686</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2394554846691313</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1702943023862044</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1786279849684313</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2541875520213244</v>
+        <v>0.486913551463572</v>
       </c>
       <c r="C4" s="4">
-        <v>0.255205264211658</v>
+        <v>0.4445784556657875</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2105341334847612</v>
+        <v>0.3903564318452806</v>
       </c>
       <c r="E4" s="4">
-        <v>89.30641821946168</v>
+        <v>88.66015971606035</v>
       </c>
       <c r="F4" s="4">
-        <v>90.04036572317686</v>
+        <v>89.12994844859698</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4192372451441888</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3126327550068919</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2087867898714555</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.9864100190325622</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>3</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.025462837527297</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6702111399505608</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6535756422943743</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,34 +7462,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3200545489656518</v>
+        <v>0.2036344914472197</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2843593806155432</v>
+        <v>0.2036344914472197</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2621429718468837</v>
+        <v>0.2033510992200054</v>
       </c>
       <c r="E3" s="4">
-        <v>86.7139899438036</v>
+        <v>89.42768411712512</v>
       </c>
       <c r="F3" s="4">
-        <v>87.92384009337616</v>
+        <v>94.61628246279543</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4386,34 +7521,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1901052592103754</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1057911891243255</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1057911891243255</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2036344914472197</v>
+        <v>0.3200545489656518</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2036344914472197</v>
+        <v>0.2843593806155432</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2033510992200054</v>
+        <v>0.2621429718468837</v>
       </c>
       <c r="E4" s="4">
-        <v>89.42768411712512</v>
+        <v>86.7139899438036</v>
       </c>
       <c r="F4" s="4">
-        <v>94.61628246279543</v>
+        <v>87.92384009337616</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2810179697299275</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1712833267473634</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1440166695133855</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.80327330824232</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>4</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.452913836028517</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>3.393319803245094</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.424946801565245</v>
+      </c>
+      <c r="R5" s="5">
+        <v>18</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,25 +7762,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.499756872095575</v>
+        <v>0.3055448175335946</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4640271716435532</v>
+        <v>0.288011318917022</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4416097558360217</v>
+        <v>0.2380422352003791</v>
       </c>
       <c r="E3" s="4">
-        <v>87.41200828157352</v>
+        <v>86.82194616977219</v>
       </c>
       <c r="F3" s="4">
-        <v>89.47135492656314</v>
+        <v>88.70732419025661</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
@@ -4599,25 +7821,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2557971510137637</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1549239451579845</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.153166888337135</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3055448175335946</v>
+        <v>0.499756872095575</v>
       </c>
       <c r="C4" s="4">
-        <v>0.288011318917022</v>
+        <v>0.4640271716435532</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2380422352003791</v>
+        <v>0.4416097558360217</v>
       </c>
       <c r="E4" s="4">
-        <v>86.82194616977219</v>
+        <v>87.41200828157352</v>
       </c>
       <c r="F4" s="4">
-        <v>88.70732419025661</v>
+        <v>89.47135492656314</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2439336513105484</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3958330257874901</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3811047960858379</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.441585035759805</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.8761339799424605</v>
+      </c>
+      <c r="O5" s="5">
+        <v>15</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.450392473830875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6353319264153574</v>
+      </c>
+      <c r="R5" s="5">
+        <v>14</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,34 +8062,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3077466161729394</v>
+        <v>0.1917187783243722</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3097071237806316</v>
+        <v>0.1917187783243722</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2893302114488183</v>
+        <v>0.1895015891989795</v>
       </c>
       <c r="E3" s="4">
-        <v>94.019520851819</v>
+        <v>95.78083407275953</v>
       </c>
       <c r="F3" s="4">
-        <v>94.69312323703872</v>
+        <v>97.53428654800116</v>
       </c>
       <c r="G3" s="5">
         <v>23</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4812,34 +8121,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1917187783243722</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04215418841909167</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04215418841909167</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1917187783243722</v>
+        <v>0.3077466161729394</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1917187783243722</v>
+        <v>0.3097071237806316</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1895015891989795</v>
+        <v>0.2893302114488183</v>
       </c>
       <c r="E4" s="4">
-        <v>95.78083407275953</v>
+        <v>94.019520851819</v>
       </c>
       <c r="F4" s="4">
-        <v>97.53428654800116</v>
+        <v>94.69312323703872</v>
       </c>
       <c r="G4" s="5">
         <v>23</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2975961230735106</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1178518934528821</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1217096761430221</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>5.290750223870907</v>
@@ -4894,9 +8239,25 @@
       <c r="M5" s="5">
         <v>3</v>
       </c>
+      <c r="N5" s="4">
+        <v>2.653184308307736</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>6.533541497655862</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8268,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.232226528717748</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2185640706194011</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.201713706125483</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.29991126885541</v>
-      </c>
-      <c r="F3" s="4">
-        <v>92.25707615990707</v>
-      </c>
-      <c r="G3" s="5">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1851081082371001</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1851081082371001</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1745217180786468</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.09671694764862</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.93230230522323</v>
-      </c>
-      <c r="G4" s="5">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5">
-        <v>23</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2.752262695312993</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1865375278308645</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4.870280901939317</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.32298136645983</v>
-      </c>
-      <c r="F5" s="4">
-        <v>85.53545374963238</v>
-      </c>
-      <c r="G5" s="5">
-        <v>23</v>
-      </c>
-      <c r="H5" s="5">
-        <v>17</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5137508471422834</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4771818723733058</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5066022427958368</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.36527654540072</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.62357747300908</v>
-      </c>
-      <c r="G3" s="5">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4027693509270174</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4027693509270174</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3351364881088384</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.1366459627329</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.11321855850579</v>
-      </c>
-      <c r="G4" s="5">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5">
-        <v>23</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2.124213279057243</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6176548895079019</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.886842912421713</v>
-      </c>
-      <c r="E5" s="4">
-        <v>84.92014196983054</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.65334111467934</v>
-      </c>
-      <c r="G5" s="5">
-        <v>23</v>
-      </c>
-      <c r="H5" s="5">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BalzarettiDensity2024.xlsx
+++ b/public/downloads/BalzarettiDensity2024.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.182212868598397</v>
+        <v>-0.1680390365302316</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08823448263430791</v>
+        <v>0.08761822906612682</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08823448263430791</v>
+        <v>0.08761822906612682</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1872295854344532</v>
+        <v>-0.1787296870730017</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.176347151067806</v>
+        <v>0.1755199961560516</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1509662314510059</v>
+        <v>0.1504399982205609</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -1675,16 +1675,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5431466319978376</v>
+        <v>0.05922058435856759</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>2.827233568209384</v>
+        <v>2.734614719224166</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4796675201016884</v>
+        <v>0.1835622370137099</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4027693509270174</v>
+        <v>-0.342937902472535</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1976753281909036</v>
+        <v>0.191672673517322</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1976753281909036</v>
+        <v>0.191672673517322</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.374320673746147</v>
+        <v>-0.3252602084130842</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4464686863409985</v>
+        <v>0.4431162611684794</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3957350461401714</v>
+        <v>0.391676847247122</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -1975,16 +1975,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>1.048868717983847</v>
+        <v>0.8257935381945885</v>
       </c>
       <c r="O5" s="5">
         <v>19</v>
       </c>
       <c r="P5" s="4">
-        <v>1.785345450467943</v>
+        <v>1.774298581092894</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.624871002076417</v>
+        <v>0.5311928212316116</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07626561580252558</v>
+        <v>-0.04982717183925445</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1303484382656246</v>
+        <v>0.1268999455747632</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1267385738573271</v>
+        <v>0.1254796003352665</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1226424180680183</v>
+        <v>-0.1827672447235074</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2289657270981218</v>
+        <v>0.2223803924184886</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2081973345686264</v>
+        <v>0.19525865119041</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.0419243259153981</v>
+        <v>-0.06907667470154077</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1408247833470345</v>
+        <v>0.1356738007852406</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1352380029532288</v>
+        <v>0.1295964506236449</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3316743715164313</v>
+        <v>-0.293215161635743</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3095483827496257</v>
+        <v>0.3038422361383334</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3095483827496257</v>
+        <v>0.3038422361383334</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -2516,13 +2516,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2269727443281266</v>
+        <v>-0.2187541174340879</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3125807646751658</v>
+        <v>0.3122234330710772</v>
       </c>
       <c r="Q4" s="4">
         <v>0.3286708917709955</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.03337470438476357</v>
+        <v>0.007952525986326009</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>9.186830853523697</v>
+        <v>9.192357414045096</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3190324805147118</v>
+        <v>0.3175370582559802</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3403551919815191</v>
+        <v>-0.2695426419439713</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1448267282279797</v>
+        <v>0.133583045535809</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1448267282279797</v>
+        <v>0.133583045535809</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.486194664158147</v>
+        <v>-0.4431427717822274</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1769514075920509</v>
+        <v>0.1793699234755022</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1795171923741293</v>
+        <v>0.1739917890010344</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -2875,20 +2875,22 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>3.481150424272764</v>
+        <v>-0.204570954802243</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>6.259767387034104</v>
-      </c>
-      <c r="Q5" s="4"/>
+        <v>4.565108441864014</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1690703429658527</v>
+      </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S5" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3055,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3581623128437336</v>
+        <v>-0.3809167470892376</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07488897875347074</v>
+        <v>0.07213985811438615</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07488897875347074</v>
+        <v>0.07213985811438615</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -3114,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3181818992112052</v>
+        <v>-0.3355849042578107</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1860634607847836</v>
+        <v>0.1840237619242551</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.167717657929043</v>
+        <v>0.1663762911678817</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -3173,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.139719624327251</v>
+        <v>-0.1078536175671303</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>2.563642963020406</v>
+        <v>2.553944613136891</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1336395813489485</v>
+        <v>0.131765110363059</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -3355,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05520139841579592</v>
+        <v>-0.04973010028877711</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1340293774571558</v>
+        <v>0.1340928732216956</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04560663031765973</v>
+        <v>0.045424316883905</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -3414,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1476921415309912</v>
+        <v>-0.1003428224550618</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2240592256819597</v>
+        <v>0.2181686084600225</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1051961309800072</v>
+        <v>0.09423504363446357</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3473,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1172092755845865</v>
+        <v>-0.1098340357131766</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1612668615911582</v>
+        <v>0.1612552114454786</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06527161081300464</v>
+        <v>0.06492419293927548</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -3655,16 +3657,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4399092111113138</v>
+        <v>-0.3458747086873544</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1591186579052093</v>
+        <v>0.1255539628424062</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1591186579052093</v>
+        <v>0.1255539628424062</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -3714,22 +3716,22 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7041955100076979</v>
+        <v>-0.6266116003076121</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1918162534185378</v>
+        <v>0.1701439350086099</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1843637563518463</v>
+        <v>0.06779833175610997</v>
       </c>
       <c r="R4" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3773,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4750851618731469</v>
+        <v>-0.5000243515925522</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1526657153039152</v>
+        <v>0.1509918743925016</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08270083600433459</v>
+        <v>0.07981731188242915</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -3955,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04767936505763382</v>
+        <v>-0.03641058581409284</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1335299633638813</v>
+        <v>0.1328647313615528</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05015249186778432</v>
+        <v>0.0489448048088254</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -4014,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1173206753229193</v>
+        <v>-0.08507585159117781</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2316573085906362</v>
+        <v>0.2279236382930841</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1156551433399861</v>
+        <v>0.1084949498015489</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -4073,13 +4075,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.06491039108442974</v>
+        <v>-0.05966214101272582</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1645768239541577</v>
+        <v>0.1648050087398839</v>
       </c>
       <c r="Q5" s="4">
         <v>0.07552735193522823</v>
@@ -4255,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2442022670084874</v>
+        <v>-0.2441505947332772</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1083722513008634</v>
+        <v>0.1083700046802021</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1083722513008634</v>
+        <v>0.1083700046802021</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -4314,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5297754165652819</v>
+        <v>-0.5467724440732411</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1924058644224035</v>
+        <v>0.191315217753822</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1856893929280466</v>
+        <v>0.1835852978837799</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -4373,16 +4375,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8531979573462709</v>
+        <v>-0.2358006158975243</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>2.887234934402152</v>
+        <v>2.36894897479515</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.131839667128553</v>
+        <v>0.1489540283513895</v>
       </c>
       <c r="R5" s="5">
         <v>16</v>
@@ -4519,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>1.776647101952246</v>
+        <v>1.776584529398776</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1498864687372405</v>
+        <v>0.1450054549651696</v>
       </c>
       <c r="J3" s="4">
-        <v>2.632486651926779</v>
+        <v>2.628869013824196</v>
       </c>
       <c r="K3" s="4">
         <v>87.45144434585463</v>
@@ -4551,13 +4553,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>86.95652173913044</v>
+        <v>85.50724637681159</v>
       </c>
       <c r="C4" s="3">
         <v>8.695652173913043</v>
       </c>
       <c r="D4" s="3">
-        <v>4.347826086956522</v>
+        <v>5.797101449275362</v>
       </c>
       <c r="E4" s="3">
         <v>2.898550724637681</v>
@@ -4566,16 +4568,16 @@
         <v>1.449275362318841</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3843793991145523</v>
+        <v>0.3681689016262041</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3613204540438006</v>
+        <v>0.3153615795243785</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3731930175369899</v>
+        <v>0.3691873577626715</v>
       </c>
       <c r="K4" s="4">
         <v>89.1195898649316</v>
@@ -4601,13 +4603,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>84.05797101449275</v>
+        <v>81.15942028985508</v>
       </c>
       <c r="C5" s="3">
         <v>10.14492753623188</v>
       </c>
       <c r="D5" s="3">
-        <v>5.797101449275362</v>
+        <v>8.695652173913043</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -4616,16 +4618,16 @@
         <v>2.898550724637681</v>
       </c>
       <c r="G5" s="3">
-        <v>2.898550724637681</v>
+        <v>5.797101449275362</v>
       </c>
       <c r="H5" s="4">
-        <v>1.223464773038928</v>
+        <v>1.023447276724732</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5263883303407146</v>
+        <v>0.1444751780441741</v>
       </c>
       <c r="J5" s="4">
-        <v>1.803729911823445</v>
+        <v>1.604311773533117</v>
       </c>
       <c r="K5" s="4">
         <v>86.8135660061122</v>
@@ -4669,13 +4671,13 @@
         <v>1.449275362318841</v>
       </c>
       <c r="H6" s="4">
-        <v>1.000383148258783</v>
+        <v>0.9251503242959745</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3625940862643418</v>
+        <v>0.2508185542682655</v>
       </c>
       <c r="J6" s="4">
-        <v>1.279385280349065</v>
+        <v>1.251962454598824</v>
       </c>
       <c r="K6" s="4">
         <v>85.21887015675816</v>
@@ -4701,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>65.21739130434783</v>
+        <v>89.85507246376811</v>
       </c>
       <c r="C7" s="3">
         <v>1.449275362318841</v>
       </c>
       <c r="D7" s="3">
-        <v>33.33333333333333</v>
+        <v>8.695652173913043</v>
       </c>
       <c r="E7" s="3">
         <v>1.449275362318841</v>
@@ -4716,16 +4718,16 @@
         <v>2.898550724637681</v>
       </c>
       <c r="G7" s="3">
-        <v>28.98550724637681</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="H7" s="4">
-        <v>2.231182526509278</v>
+        <v>1.814799475425088</v>
       </c>
       <c r="I7" s="4">
-        <v>0.08104798241745767</v>
+        <v>0.09252532961925933</v>
       </c>
       <c r="J7" s="4">
-        <v>2.473244452480268</v>
+        <v>2.059281888399164</v>
       </c>
       <c r="K7" s="4">
         <v>93.33629103815387</v>
@@ -4769,13 +4771,13 @@
         <v>1.449275362318841</v>
       </c>
       <c r="H8" s="4">
-        <v>1.030605067303833</v>
+        <v>0.9992509814821149</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2200510928556317</v>
+        <v>0.13574295436942</v>
       </c>
       <c r="J8" s="4">
-        <v>1.721233833278414</v>
+        <v>1.703775917395411</v>
       </c>
       <c r="K8" s="4">
         <v>89.2398698609876</v>
@@ -4819,13 +4821,13 @@
         <v>2.898550724637681</v>
       </c>
       <c r="H9" s="4">
-        <v>0.8098298216666148</v>
+        <v>0.8030291719262316</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3845475501754768</v>
+        <v>0.3539086364327309</v>
       </c>
       <c r="J9" s="4">
-        <v>1.048212772214983</v>
+        <v>1.052266792958664</v>
       </c>
       <c r="K9" s="4">
         <v>86.14068815932139</v>
@@ -4869,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1667129829035937</v>
+        <v>0.1616513795928308</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1567246371263941</v>
+        <v>0.1501115673831072</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1658106429217215</v>
+        <v>0.1657458467340577</v>
       </c>
       <c r="K10" s="4">
         <v>80.38006506950582</v>
@@ -4919,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>3.269653333649496</v>
+        <v>3.269474361084836</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3186097134568567</v>
+        <v>0.315998654282554</v>
       </c>
       <c r="J11" s="4">
-        <v>3.77266916027253</v>
+        <v>3.772169256420794</v>
       </c>
       <c r="K11" s="4">
         <v>88.05925268658189</v>
@@ -4951,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>57.97101449275362</v>
+        <v>81.15942028985508</v>
       </c>
       <c r="C12" s="3">
         <v>8.695652173913043</v>
       </c>
       <c r="D12" s="3">
-        <v>33.33333333333333</v>
+        <v>10.14492753623188</v>
       </c>
       <c r="E12" s="3">
         <v>2.898550724637681</v>
@@ -4966,16 +4968,16 @@
         <v>1.449275362318841</v>
       </c>
       <c r="G12" s="3">
-        <v>28.98550724637681</v>
+        <v>5.797101449275362</v>
       </c>
       <c r="H12" s="4">
-        <v>2.193848507618045</v>
+        <v>1.626020470291775</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1595701754900933</v>
+        <v>0.1559892133534792</v>
       </c>
       <c r="J12" s="4">
-        <v>2.335534379116866</v>
+        <v>1.766628115042681</v>
       </c>
       <c r="K12" s="4">
         <v>88.0636892438132</v>
@@ -5019,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.9415318008528869</v>
+        <v>0.9367027443918442</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1239372236887241</v>
+        <v>0.1219274519112304</v>
       </c>
       <c r="J13" s="4">
-        <v>2.220441904580213</v>
+        <v>2.217702045550239</v>
       </c>
       <c r="K13" s="4">
         <v>86.75293305728061</v>
@@ -5069,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1731184882434246</v>
+        <v>0.1711722310423989</v>
       </c>
       <c r="I14" s="4">
-        <v>0.07151446239161181</v>
+        <v>0.06779389434513393</v>
       </c>
       <c r="J14" s="4">
-        <v>0.08056084749832358</v>
+        <v>0.07732907515425054</v>
       </c>
       <c r="K14" s="4">
         <v>94.09592822636226</v>
@@ -5101,13 +5103,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>97.10144927536231</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C15" s="3">
         <v>1.449275362318841</v>
       </c>
       <c r="D15" s="3">
-        <v>1.449275362318841</v>
+        <v>2.898550724637681</v>
       </c>
       <c r="E15" s="3">
         <v>1.449275362318841</v>
@@ -5116,16 +5118,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1678668755425541</v>
+        <v>0.1488965907478392</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1423156740844149</v>
+        <v>0.09193162081313778</v>
       </c>
       <c r="J15" s="4">
-        <v>0.312975710477976</v>
+        <v>0.2906427840536246</v>
       </c>
       <c r="K15" s="4">
         <v>88.47875382036879</v>
@@ -5169,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1765880319695585</v>
+        <v>0.1751977927981736</v>
       </c>
       <c r="I16" s="4">
-        <v>0.0799033011354767</v>
+        <v>0.07718125221848779</v>
       </c>
       <c r="J16" s="4">
-        <v>0.0865688775513561</v>
+        <v>0.08454396735098899</v>
       </c>
       <c r="K16" s="4">
         <v>90.07492852213281</v>
@@ -5219,13 +5221,13 @@
         <v>2.898550724637681</v>
       </c>
       <c r="H17" s="4">
-        <v>1.062671016708473</v>
+        <v>0.8895447324097249</v>
       </c>
       <c r="I17" s="4">
-        <v>0.412131937500638</v>
+        <v>0.1448725511685166</v>
       </c>
       <c r="J17" s="4">
-        <v>1.625687578605793</v>
+        <v>1.480126299709478</v>
       </c>
       <c r="K17" s="4">
         <v>83.63994873311621</v>
@@ -6152,13 +6154,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5">
         <v>6</v>
       </c>
       <c r="D4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="5">
         <v>2</v>
@@ -6167,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5">
         <v>2</v>
@@ -6196,13 +6198,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="5">
         <v>7</v>
       </c>
       <c r="D5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -6211,7 +6213,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6284,13 +6286,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -6299,7 +6301,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
@@ -6504,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C12" s="5">
         <v>6</v>
       </c>
       <c r="D12" s="5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E12" s="5">
         <v>2</v>
@@ -6519,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H12" s="5">
         <v>2</v>
@@ -6636,13 +6638,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" s="5">
         <v>1</v>
       </c>
       <c r="D15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -6651,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="5">
         <v>1</v>
@@ -6922,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2576568053330923</v>
+        <v>-0.2643646381884821</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08962835366822133</v>
+        <v>0.08933670876146524</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08962835366822133</v>
+        <v>0.08933670876146524</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -6981,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2101089213911148</v>
+        <v>-0.1381830502539003</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1813410370505492</v>
+        <v>0.1788085256475049</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.16665425142422</v>
+        <v>0.1529529826401369</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -7040,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2678435010587066</v>
+        <v>0.2557158832715061</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>5.058971915137966</v>
+        <v>5.061608353787357</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2116853506694671</v>
+        <v>0.2109719613878671</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -7222,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2394554846691313</v>
+        <v>-0.23854829472657</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1702943023862044</v>
+        <v>0.1702548593452234</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1786279849684313</v>
+        <v>0.1785847854473569</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -7281,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4192372451441888</v>
+        <v>-0.4296810261328119</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3126327550068919</v>
+        <v>0.312178677572604</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2087867898714555</v>
+        <v>0.2081724498133013</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -7340,22 +7342,22 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>1.025462837527297</v>
+        <v>0.7826430300854383</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6702111399505608</v>
+        <v>0.6220731679607848</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6535756422943743</v>
+        <v>0.5389105262246532</v>
       </c>
       <c r="R5" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7522,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1901052592103754</v>
+        <v>-0.203179084239693</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1057911891243255</v>
+        <v>0.1044366893085588</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1057911891243255</v>
+        <v>0.1044366893085588</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -7581,16 +7583,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2810179697299275</v>
+        <v>-0.2436801875036565</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1712833267473634</v>
+        <v>0.1696599449114386</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1440166695133855</v>
+        <v>0.1418203293824284</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -7640,22 +7642,22 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>1.452913836028517</v>
+        <v>0.04877435644038286</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>3.393319803245094</v>
+        <v>2.796245195954199</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.424946801565245</v>
+        <v>0.2048512823047259</v>
       </c>
       <c r="R5" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7822,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2557971510137637</v>
+        <v>-0.3160173198294096</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1549239451579845</v>
+        <v>0.1326466648057607</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.153166888337135</v>
+        <v>0.1365810412544246</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -7881,16 +7883,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2439336513105484</v>
+        <v>-0.392033414399414</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3958330257874901</v>
+        <v>0.3514415413663371</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3811047960858379</v>
+        <v>0.3522695534648417</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -7940,16 +7942,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8761339799424605</v>
+        <v>0.3862094232531774</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>2.450392473830875</v>
+        <v>2.291362766715826</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6353319264153574</v>
+        <v>0.2690850025786438</v>
       </c>
       <c r="R5" s="5">
         <v>14</v>
@@ -8122,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1917187783243722</v>
+        <v>-0.193447754424426</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04215418841909167</v>
+        <v>0.04207901554517628</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04215418841909167</v>
+        <v>0.04207901554517628</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -8181,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2975961230735106</v>
+        <v>-0.2856758554736345</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1178518934528821</v>
+        <v>0.1173336209485396</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1217096761430221</v>
@@ -8240,20 +8242,22 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>2.653184308307736</v>
+        <v>-0.131157821760258</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>6.533541497655862</v>
-      </c>
-      <c r="Q5" s="4"/>
+        <v>5.284985789781549</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1230082472769728</v>
+      </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S5" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
